--- a/Data Wisudawan fix.xlsx
+++ b/Data Wisudawan fix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/78651E42104D7AE2/penting/dasar pemograman/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\OneDrive\Documents\DASAR PEMROGRAMAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{CA57065B-D047-4CE8-9705-4928E0B3B1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{321312A7-844B-49C3-AF70-AB9B42C79C03}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99847C19-3D61-45CC-A3D1-D19C290928FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3FBF1DF3-F98D-4F82-A374-D46FFEA82B89}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3FBF1DF3-F98D-4F82-A374-D46FFEA82B89}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -23,12 +23,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="177">
   <si>
     <t>NIM</t>
   </si>
@@ -552,40 +561,13 @@
     <t>Farhan Pratama</t>
   </si>
   <si>
-    <t>agus</t>
-  </si>
-  <si>
-    <t>sinta permata</t>
-  </si>
-  <si>
-    <t>BUDI MAULANA</t>
-  </si>
-  <si>
-    <t>AULIA PERMATA</t>
-  </si>
-  <si>
-    <t>winda</t>
-  </si>
-  <si>
-    <t>mega nugroho</t>
-  </si>
-  <si>
-    <t>rina sari kurniawan</t>
-  </si>
-  <si>
-    <t>budi wijaya</t>
-  </si>
-  <si>
-    <t>nina</t>
-  </si>
-  <si>
-    <t>rafi</t>
-  </si>
-  <si>
-    <t>VINA ANJANI</t>
-  </si>
-  <si>
-    <t>PUTRI</t>
+    <t>Vina Anjani</t>
+  </si>
+  <si>
+    <t>Budi Wijaya</t>
+  </si>
+  <si>
+    <t>Aulia Permata</t>
   </si>
 </sst>
 </file>
@@ -638,58 +620,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -703,9 +634,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -743,7 +674,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -849,7 +780,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -991,7 +922,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1000,17 +931,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C56FC46-ED8E-4F86-8EB3-620BF8D6B1DA}">
   <dimension ref="A1:F207"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
-    <col min="2" max="2" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.81640625" customWidth="1"/>
+    <col min="2" max="2" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
+    <col min="6" max="6" width="8.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1030,7 +961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>231015</v>
       </c>
@@ -1050,7 +981,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>231018</v>
       </c>
@@ -1070,7 +1001,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>231027</v>
       </c>
@@ -1090,7 +1021,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>231044</v>
       </c>
@@ -1110,7 +1041,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>231094</v>
       </c>
@@ -1130,7 +1061,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>231121</v>
       </c>
@@ -1150,7 +1081,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>231138</v>
       </c>
@@ -1170,7 +1101,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>231200</v>
       </c>
@@ -1190,7 +1121,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>231244</v>
       </c>
@@ -1210,7 +1141,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>231271</v>
       </c>
@@ -1230,7 +1161,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>231274</v>
       </c>
@@ -1250,7 +1181,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>231304</v>
       </c>
@@ -1270,7 +1201,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>231311</v>
       </c>
@@ -1290,7 +1221,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>231314</v>
       </c>
@@ -1310,12 +1241,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>231341</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
@@ -1330,7 +1261,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>231019</v>
       </c>
@@ -1350,7 +1281,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>231046</v>
       </c>
@@ -1370,7 +1301,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>231047</v>
       </c>
@@ -1390,7 +1321,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>231055</v>
       </c>
@@ -1410,7 +1341,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>231064</v>
       </c>
@@ -1430,7 +1361,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>231134</v>
       </c>
@@ -1450,7 +1381,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>231144</v>
       </c>
@@ -1470,7 +1401,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>231163</v>
       </c>
@@ -1490,7 +1421,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>231170</v>
       </c>
@@ -1510,7 +1441,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>231194</v>
       </c>
@@ -1530,7 +1461,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>231223</v>
       </c>
@@ -1550,7 +1481,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>231242</v>
       </c>
@@ -1570,7 +1501,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>231259</v>
       </c>
@@ -1590,7 +1521,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>231284</v>
       </c>
@@ -1610,12 +1541,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>231297</v>
       </c>
       <c r="B31" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
         <v>26</v>
@@ -1630,7 +1561,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>231299</v>
       </c>
@@ -1650,7 +1581,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>231308</v>
       </c>
@@ -1670,7 +1601,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>231346</v>
       </c>
@@ -1690,7 +1621,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>231349</v>
       </c>
@@ -1710,7 +1641,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>231002</v>
       </c>
@@ -1730,12 +1661,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>231009</v>
       </c>
       <c r="B37" t="s">
-        <v>174</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
@@ -1750,12 +1681,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>231056</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
@@ -1770,7 +1701,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>231105</v>
       </c>
@@ -1790,7 +1721,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>231116</v>
       </c>
@@ -1810,7 +1741,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>231118</v>
       </c>
@@ -1830,7 +1761,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>231130</v>
       </c>
@@ -1850,7 +1781,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>231133</v>
       </c>
@@ -1870,7 +1801,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>231141</v>
       </c>
@@ -1890,7 +1821,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>231147</v>
       </c>
@@ -1910,7 +1841,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>231149</v>
       </c>
@@ -1930,7 +1861,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>231168</v>
       </c>
@@ -1950,7 +1881,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>231186</v>
       </c>
@@ -1970,7 +1901,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>231188</v>
       </c>
@@ -1990,7 +1921,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>231198</v>
       </c>
@@ -2010,7 +1941,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>231219</v>
       </c>
@@ -2030,7 +1961,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>231230</v>
       </c>
@@ -2050,7 +1981,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>231238</v>
       </c>
@@ -2070,7 +2001,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>231276</v>
       </c>
@@ -2090,7 +2021,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>231285</v>
       </c>
@@ -2110,7 +2041,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>231310</v>
       </c>
@@ -2130,7 +2061,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>231318</v>
       </c>
@@ -2150,7 +2081,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>231005</v>
       </c>
@@ -2170,12 +2101,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>231011</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
         <v>15</v>
@@ -2190,7 +2121,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>231033</v>
       </c>
@@ -2210,7 +2141,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>231036</v>
       </c>
@@ -2230,7 +2161,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>231095</v>
       </c>
@@ -2250,7 +2181,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>231111</v>
       </c>
@@ -2270,7 +2201,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>231120</v>
       </c>
@@ -2290,7 +2221,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>231156</v>
       </c>
@@ -2310,7 +2241,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>231162</v>
       </c>
@@ -2330,7 +2261,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>231201</v>
       </c>
@@ -2350,7 +2281,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>231246</v>
       </c>
@@ -2370,7 +2301,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>231280</v>
       </c>
@@ -2390,7 +2321,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>231336</v>
       </c>
@@ -2410,7 +2341,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>231357</v>
       </c>
@@ -2430,7 +2361,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>231045</v>
       </c>
@@ -2450,7 +2381,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>231048</v>
       </c>
@@ -2470,7 +2401,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>231062</v>
       </c>
@@ -2490,7 +2421,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>231102</v>
       </c>
@@ -2510,7 +2441,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>231106</v>
       </c>
@@ -2530,7 +2461,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>231114</v>
       </c>
@@ -2550,7 +2481,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>231125</v>
       </c>
@@ -2570,7 +2501,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>231204</v>
       </c>
@@ -2590,7 +2521,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>231243</v>
       </c>
@@ -2610,7 +2541,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>231255</v>
       </c>
@@ -2630,7 +2561,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>231290</v>
       </c>
@@ -2650,7 +2581,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>231348</v>
       </c>
@@ -2670,7 +2601,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>231303</v>
       </c>
@@ -2690,7 +2621,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>231001</v>
       </c>
@@ -2710,7 +2641,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>231040</v>
       </c>
@@ -2730,7 +2661,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>231059</v>
       </c>
@@ -2750,7 +2681,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>231080</v>
       </c>
@@ -2770,7 +2701,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>231104</v>
       </c>
@@ -2790,7 +2721,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>231146</v>
       </c>
@@ -2810,7 +2741,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>231222</v>
       </c>
@@ -2830,7 +2761,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>231228</v>
       </c>
@@ -2850,7 +2781,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>231231</v>
       </c>
@@ -2870,7 +2801,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>231232</v>
       </c>
@@ -2890,7 +2821,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>231233</v>
       </c>
@@ -2910,7 +2841,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>231236</v>
       </c>
@@ -2930,7 +2861,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>231024</v>
       </c>
@@ -2950,7 +2881,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>231050</v>
       </c>
@@ -2970,7 +2901,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>231078</v>
       </c>
@@ -2990,7 +2921,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>231083</v>
       </c>
@@ -3010,12 +2941,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>231140</v>
       </c>
       <c r="B101" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C101" t="s">
         <v>11</v>
@@ -3030,7 +2961,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>231157</v>
       </c>
@@ -3050,7 +2981,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>231161</v>
       </c>
@@ -3070,7 +3001,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>231164</v>
       </c>
@@ -3090,7 +3021,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>231173</v>
       </c>
@@ -3110,7 +3041,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>231213</v>
       </c>
@@ -3130,7 +3061,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>231251</v>
       </c>
@@ -3150,7 +3081,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>231296</v>
       </c>
@@ -3170,7 +3101,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>231327</v>
       </c>
@@ -3190,7 +3121,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>231350</v>
       </c>
@@ -3210,12 +3141,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>231359</v>
       </c>
       <c r="B111" t="s">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="C111" t="s">
         <v>11</v>
@@ -3230,7 +3161,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>231225</v>
       </c>
@@ -3250,7 +3181,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>231004</v>
       </c>
@@ -3270,7 +3201,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>231031</v>
       </c>
@@ -3290,7 +3221,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>231037</v>
       </c>
@@ -3310,7 +3241,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>231107</v>
       </c>
@@ -3330,7 +3261,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>231142</v>
       </c>
@@ -3350,7 +3281,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>231179</v>
       </c>
@@ -3370,7 +3301,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>231203</v>
       </c>
@@ -3390,7 +3321,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>231206</v>
       </c>
@@ -3410,7 +3341,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>231207</v>
       </c>
@@ -3430,7 +3361,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>231210</v>
       </c>
@@ -3450,7 +3381,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>231240</v>
       </c>
@@ -3470,7 +3401,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>231250</v>
       </c>
@@ -3490,7 +3421,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>231256</v>
       </c>
@@ -3510,7 +3441,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>231264</v>
       </c>
@@ -3530,7 +3461,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>231288</v>
       </c>
@@ -3550,7 +3481,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>231289</v>
       </c>
@@ -3570,7 +3501,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>231294</v>
       </c>
@@ -3590,7 +3521,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>231312</v>
       </c>
@@ -3610,7 +3541,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>231329</v>
       </c>
@@ -3630,7 +3561,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>231026</v>
       </c>
@@ -3650,7 +3581,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>231035</v>
       </c>
@@ -3670,12 +3601,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>231049</v>
       </c>
       <c r="B134" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C134" t="s">
         <v>31</v>
@@ -3690,12 +3621,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>231052</v>
       </c>
       <c r="B135" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C135" t="s">
         <v>31</v>
@@ -3710,7 +3641,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>231077</v>
       </c>
@@ -3730,12 +3661,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>231091</v>
       </c>
       <c r="B137" t="s">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="C137" t="s">
         <v>31</v>
@@ -3750,7 +3681,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>231097</v>
       </c>
@@ -3770,7 +3701,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>231150</v>
       </c>
@@ -3790,7 +3721,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>231155</v>
       </c>
@@ -3810,7 +3741,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>231192</v>
       </c>
@@ -3830,7 +3761,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>231208</v>
       </c>
@@ -3850,7 +3781,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>231224</v>
       </c>
@@ -3870,7 +3801,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>231247</v>
       </c>
@@ -3890,7 +3821,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>231275</v>
       </c>
@@ -3910,7 +3841,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>231293</v>
       </c>
@@ -3930,7 +3861,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>231305</v>
       </c>
@@ -3950,7 +3881,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>231319</v>
       </c>
@@ -3970,7 +3901,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>231321</v>
       </c>
@@ -3990,7 +3921,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>231330</v>
       </c>
@@ -4010,7 +3941,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>231342</v>
       </c>
@@ -4030,7 +3961,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>231343</v>
       </c>
@@ -4050,7 +3981,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>231022</v>
       </c>
@@ -4070,7 +4001,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>231070</v>
       </c>
@@ -4090,7 +4021,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>231074</v>
       </c>
@@ -4110,7 +4041,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>231081</v>
       </c>
@@ -4130,7 +4061,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>231084</v>
       </c>
@@ -4150,7 +4081,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>231088</v>
       </c>
@@ -4170,7 +4101,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>231098</v>
       </c>
@@ -4190,7 +4121,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>231101</v>
       </c>
@@ -4210,7 +4141,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>231143</v>
       </c>
@@ -4230,7 +4161,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>231214</v>
       </c>
@@ -4250,7 +4181,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>231215</v>
       </c>
@@ -4270,7 +4201,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>231226</v>
       </c>
@@ -4290,7 +4221,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>231245</v>
       </c>
@@ -4310,12 +4241,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>231272</v>
       </c>
       <c r="B166" t="s">
-        <v>182</v>
+        <v>45</v>
       </c>
       <c r="C166" t="s">
         <v>18</v>
@@ -4330,7 +4261,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>231286</v>
       </c>
@@ -4350,7 +4281,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>231338</v>
       </c>
@@ -4370,7 +4301,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>231013</v>
       </c>
@@ -4390,7 +4321,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>231038</v>
       </c>
@@ -4410,7 +4341,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>231058</v>
       </c>
@@ -4430,7 +4361,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>231067</v>
       </c>
@@ -4450,7 +4381,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>231082</v>
       </c>
@@ -4470,7 +4401,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>231115</v>
       </c>
@@ -4490,7 +4421,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>231123</v>
       </c>
@@ -4510,7 +4441,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>231217</v>
       </c>
@@ -4530,7 +4461,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>231218</v>
       </c>
@@ -4550,7 +4481,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>231235</v>
       </c>
@@ -4570,7 +4501,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>231260</v>
       </c>
@@ -4590,7 +4521,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>231287</v>
       </c>
@@ -4610,7 +4541,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>231291</v>
       </c>
@@ -4630,7 +4561,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>231354</v>
       </c>
@@ -4650,7 +4581,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>231006</v>
       </c>
@@ -4670,7 +4601,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>231028</v>
       </c>
@@ -4690,7 +4621,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>231039</v>
       </c>
@@ -4710,7 +4641,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>231075</v>
       </c>
@@ -4730,7 +4661,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>231119</v>
       </c>
@@ -4750,7 +4681,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>231191</v>
       </c>
@@ -4770,7 +4701,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>231267</v>
       </c>
@@ -4790,7 +4721,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>231301</v>
       </c>
@@ -4810,7 +4741,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>231309</v>
       </c>
@@ -4830,7 +4761,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>231317</v>
       </c>
@@ -4850,7 +4781,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>231017</v>
       </c>
@@ -4870,7 +4801,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>231025</v>
       </c>
@@ -4890,7 +4821,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>231032</v>
       </c>
@@ -4910,7 +4841,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>231054</v>
       </c>
@@ -4930,7 +4861,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>231060</v>
       </c>
@@ -4950,7 +4881,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>231089</v>
       </c>
@@ -4970,12 +4901,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>231090</v>
       </c>
       <c r="B199" t="s">
-        <v>179</v>
+        <v>52</v>
       </c>
       <c r="C199" t="s">
         <v>28</v>
@@ -4990,7 +4921,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>231112</v>
       </c>
@@ -5010,7 +4941,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>231122</v>
       </c>
@@ -5030,7 +4961,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>231124</v>
       </c>
@@ -5050,7 +4981,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>231180</v>
       </c>
@@ -5070,7 +5001,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>231292</v>
       </c>
@@ -5090,7 +5021,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>231337</v>
       </c>
@@ -5110,7 +5041,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>231339</v>
       </c>
@@ -5130,7 +5061,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>231352</v>
       </c>
